--- a/光伏配储项目/电价数据/2026/经贸站.xlsx
+++ b/光伏配储项目/电价数据/2026/经贸站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.94545</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.24008</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.05438</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5907899999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.88854</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.53266</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45906</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42452</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40445</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44689</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5012099999999999</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12258</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13477</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14089</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07368999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11355</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.5418099999999999</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.21226</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28696</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05088</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7652</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.1925</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1478</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21923</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22942</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23467</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21864</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.6796</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14877</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.53091</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7740900000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.95578</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7310800000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.65996</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65822</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.18501</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.79289</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.52142</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.37239</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.60193</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.7608400000000001</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.00428</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.06217</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.78918</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.32795</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.87118</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79648</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75705</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51755</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47952</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46887</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42537</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7082000000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76904</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8712300000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91595</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49426</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5146900000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50257</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48507</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46719</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8765599999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.71985</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.81532</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42614</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50869</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50571</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77685</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52125</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8882899999999999</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.84461</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49618</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.72321</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.31005</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.07514</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.02458</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46961</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49773</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52212</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.92206</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62225</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.95129</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.33114</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.55164</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17674</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.12441</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.59772</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.4999</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.65528</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.43358</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.48481</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.04157</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.37728</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90211</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.46098</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.55375</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.36676</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.15047</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78696</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80777</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44898</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3346</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50768</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48673</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48716</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44758</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44306</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47207</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.50413</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.68798</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.9051</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.82077</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.75903</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.25041</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55372</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.49526</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8178300000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.59084</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72305</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81159</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5278400000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.54763</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7990499999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.23325</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.68188</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.59773</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49346</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.44545</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.7869700000000001</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52093</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50413</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57009</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5953099999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54259</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56243</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26489</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61629</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.18212</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.50432</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5348999999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57592</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.97734</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.03984</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.40754</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.86314</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.8380700000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.67608</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.93032</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6102300000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.9077000000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56259</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.31374</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.87271</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5593899999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48191</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6156200000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.51488</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34195</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52163</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49373</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.52606</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.76263</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.6422899999999999</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8817999999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.21757</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.80911</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.9407000000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.42301</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.7050599999999999</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.43702</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.27662</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.18755</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.02995</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.5223</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.97694</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60434</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47979</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.95625</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.95984</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.84184</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.4023</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.4759</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42798</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49517</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46173</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47411</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51973</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.03893</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.93833</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.46864</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.00489</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.89318</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50074</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.7651100000000001</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.65344</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.5463899999999999</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31754</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7236900000000001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.8476699999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.44397</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.19828</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.21991</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15558</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27053</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18918</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5134099999999999</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.48645</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22407</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21014</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06344</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.10197</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.00102</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.04135</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26976</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46142</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48662</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34442</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.5911900000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40633</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.27269</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10275</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01524</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21616</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05422</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20504</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.06595000000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07031</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06855</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33161</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3131</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78523</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87758</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.1603</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.8474700000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40942</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42682</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.56008</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5849800000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70925</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8766900000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46657</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55347</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.81976</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5728</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8532799999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.63186</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6344</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5924199999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.30204</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28884</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42465</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34724</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91407</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44504</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40783</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.46381</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18835</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1978</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2538</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.11194</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42039</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44062</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.53684</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.86758</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.4438</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14002</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68716</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77749</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6388400000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.50944</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49063</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4308999999999999</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46472</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40522</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4264</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40749</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48705</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.52566</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.23172</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15514</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25996</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25306</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5440700000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.78971</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4358399999999999</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3083</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.24785</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.24244</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27703</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22916</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23638</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.23188</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.23874</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24603</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26392</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42308</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4382200000000001</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33547</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.49422</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.42113</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30172</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.9232</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.86077</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25181</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23952</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.52611</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.54653</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.4243</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.59776</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.5465599999999999</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.8553500000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.92787</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.41246</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.88278</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.11979</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.77475</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.15541</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.45936</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.43379</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.72894</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.48262</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34944</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.46363</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47618</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.69926</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.81059</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.7987000000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.5179</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.7324700000000001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.4653</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.1421</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.81441</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.7982899999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.10803</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.76898</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.30358</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.17426</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.20938</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.72001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.13197</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.31164</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.6193</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.48971</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.29125</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.531</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.68933</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.55261</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.70593</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.3011</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.60638</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.04329</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.77859</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.37435</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.7864</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.7530800000000001</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.84177</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.76871</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.76395</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.33185</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.8904299999999999</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.74154</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.87039</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.8523200000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.1271</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.79948</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.66346</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.61453</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5222899999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50382</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24114</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>1.60142</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31261</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.93591</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.08809</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.49788</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.87824</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.23527</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47566</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.14743</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.53365</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.90365</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.90063</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34351</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75259</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.32528</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.42168</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.5503400000000001</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.49865</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.59237</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.42257</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.50854</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.6339</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65103</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42948</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.6999099999999999</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.62654</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.9063600000000001</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.7222799999999999</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.47818</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.48298</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.88479</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.5857899999999999</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.9497599999999999</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.47832</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.69036</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.01508</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.39541</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.71369</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.43934</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.7652</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.57989</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.9293400000000001</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.7940199999999999</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.37176</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.7400099999999999</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.7179800000000001</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.99226</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.74773</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.98476</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.44347</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.4173</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.44811</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.0496</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.00741</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.43666</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.91896</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.10967</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9313400000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.8941699999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.80548</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.49183</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.41269</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.7726499999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40829</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35112</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5302</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47656</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.62056</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.50634</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46146</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42225</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45853</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.59976</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.3199</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.97627</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.36714</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.40376</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.48345</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42836</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.91204</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.9132899999999999</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.93476</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.60073</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.8247000000000001</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.85598</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.84709</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.92643</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.17557</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.20945</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.54043</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.89997</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.90137</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.8917200000000001</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.8909400000000001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.4597</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4217</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.47404</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5073</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.62582</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7347899999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8241799999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.59178</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.71621</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.10965</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.44118</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7369199999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76532</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6664500000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.64382</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.03016</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44967</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43908</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50764</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40667</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41766</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4377799999999999</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.90706</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.8766</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.87322</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.89335</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.88244</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1.39358</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.8944099999999999</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.97366</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.93102</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.98373</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15256</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21733</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.90349</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42514</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42586</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.33365</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46161</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.57808</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.28553</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.26272</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.26177</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.25676</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.2839100000000001</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.25208</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.1898</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24492</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27339</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26164</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09931</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03473</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19389</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24876</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25851</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27591</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43831</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.67191</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.6747300000000001</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.43151</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.50708</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32495</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.1616</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.27508</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.24419</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.24368</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.24633</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.24632</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.24501</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.23977</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.24335</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.24383</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.24362</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25058</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16701</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26716</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21416</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01295</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00023</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14591</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01536</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02924</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03822</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01885</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03614</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20153</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26488</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24766</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.33213</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.73827</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.63506</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.43133</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41579</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42509</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26357</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24512</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26957</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26611</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26995</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6840599999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8416399999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87719</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85096</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11426</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21732</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26599</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27105</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27368</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05974</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25502</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47124</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.5013</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.7921699999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.74679</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.77091</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34253</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.98049</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.76274</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.83524</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.7944199999999999</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84038</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83858</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84289</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94008</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.75471</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.79038</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7577</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36406</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.61188</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.66092</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5735800000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49377</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.46269</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.4768</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.46301</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.47478</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.45199</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26638</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.45398</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.71648</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.5911900000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.45901</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42066</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.47248</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33823</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.42065</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.40686</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.55408</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.76458</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.53969</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5010599999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.55459</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.44699</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.47652</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.61049</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.57652</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.6006900000000001</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.6498200000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.48422</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.56437</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.5851799999999999</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.79935</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.9133300000000001</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.32586</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.38727</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.05316</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.48778</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.71734</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.71196</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.55869</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.45763</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.45591</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.9320900000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.25373</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.5361</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.64996</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.52525</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35269</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.4575</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.8633099999999999</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.50154</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.96999</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.46058</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.74752</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.57639</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51212</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.17876</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7077599999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.63925</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47568</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.26129</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.47192</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.36621</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.29029</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.83251</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>1.08472</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.9945700000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.49051</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35707</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.23346</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.5686599999999999</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.80992</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>1.64341</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.8458</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.6774600000000001</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.81425</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.7838099999999999</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.90532</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.81023</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.83084</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.5909800000000001</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.49321</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.58788</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.51433</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.52752</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.87754</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.73833</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.8960199999999999</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.92237</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.77988</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48551</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.9551000000000001</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.90359</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.94186</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.90643</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.63938</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.52227</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.42502</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.68424</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36378</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.41128</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.25546</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5592699999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.7847799999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.61997</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.4067</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.52573</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.06506</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.7355</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.0194</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.5662999999999999</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.54279</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.63102</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.92077</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.7793600000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.7289600000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.54888</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.53959</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.71983</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.7447699999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.9741000000000001</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.30509</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.14389</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.63517</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35897</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.37149</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.36556</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.35543</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>1.34952</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17558</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14526</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19792</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14172</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04456</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12129</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22579</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15086</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14373</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.19573</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>1.30407</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22606</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.26199</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15292</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19665</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.63962</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.08059</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.52081</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.53837</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.68613</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>1.08277</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.7038300000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.5144299999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.77228</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5646599999999999</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5720499999999999</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.54906</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.67638</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5577799999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5515599999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.61491</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38453</v>
       </c>
     </row>
   </sheetData>
